--- a/data/historical_csv/footiqo/world_cup_football_data.xlsx
+++ b/data/historical_csv/footiqo/world_cup_football_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee16c21b72f3fde9/Documents/Football Fortunes/All data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{9D3D8A05-EEFD-4F90-A3C5-55C1E757FCE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFAAA261-4024-4339-887D-3A027308D725}"/>
+  <xr:revisionPtr revIDLastSave="425" documentId="8_{9D3D8A05-EEFD-4F90-A3C5-55C1E757FCE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6BA416B-7A55-4885-A705-AFB31F1A53FA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{95D741F4-B12C-45C7-A97C-F95A56A544CF}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3024" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3152" uniqueCount="267">
   <si>
     <t>Home</t>
   </si>
@@ -1235,7 +1235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F33CE9-0917-4340-92ED-8B6CE132D95A}">
-  <dimension ref="A1:AP73"/>
+  <dimension ref="A1:AP105"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.54296875" bestFit="1" customWidth="1"/>
@@ -1266,8 +1266,7 @@
     <col min="27" max="27" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="3.36328125" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="9" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="31" max="36" width="7.1796875" customWidth="1"/>
     <col min="37" max="38" width="6.26953125" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="6.1796875" bestFit="1" customWidth="1"/>
     <col min="40" max="42" width="6.26953125" bestFit="1" customWidth="1"/>
@@ -9753,10 +9752,3800 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
+    <row r="74" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>266</v>
+      </c>
+      <c r="B74" t="s">
+        <v>85</v>
+      </c>
+      <c r="C74" t="s">
+        <v>258</v>
+      </c>
+      <c r="D74" s="1">
+        <v>46201</v>
+      </c>
+      <c r="E74" s="7">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>1</v>
+      </c>
+      <c r="P74" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q74">
+        <v>6</v>
+      </c>
+      <c r="R74">
+        <v>12</v>
+      </c>
+      <c r="S74">
+        <v>1</v>
+      </c>
+      <c r="T74">
+        <v>7</v>
+      </c>
+      <c r="U74">
+        <v>10</v>
+      </c>
+      <c r="V74">
+        <v>16</v>
+      </c>
+      <c r="W74">
+        <v>1</v>
+      </c>
+      <c r="X74">
+        <v>4</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
+      </c>
+      <c r="Z74">
+        <v>2</v>
+      </c>
+      <c r="AA74">
+        <v>0</v>
+      </c>
+      <c r="AB74">
+        <v>0</v>
+      </c>
+      <c r="AC74">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AD74">
+        <v>1.38</v>
+      </c>
+      <c r="AE74">
+        <v>5</v>
+      </c>
+      <c r="AF74">
+        <v>3.25</v>
+      </c>
+      <c r="AG74">
+        <v>1.83</v>
+      </c>
+      <c r="AH74">
+        <v>5.3</v>
+      </c>
+      <c r="AI74">
+        <v>3.45</v>
+      </c>
+      <c r="AJ74">
+        <v>1.89</v>
+      </c>
+      <c r="AK74">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AL74">
+        <v>3.5</v>
+      </c>
+      <c r="AM74">
+        <v>1.85</v>
+      </c>
+      <c r="AN74">
+        <v>4.68</v>
+      </c>
+      <c r="AO74">
+        <v>3.3</v>
+      </c>
+      <c r="AP74">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="75" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>266</v>
+      </c>
+      <c r="B75" t="s">
+        <v>128</v>
+      </c>
+      <c r="C75" t="s">
+        <v>160</v>
+      </c>
+      <c r="D75" s="1">
+        <v>46202</v>
+      </c>
+      <c r="E75" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="F75">
+        <v>2</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+      <c r="J75">
+        <v>2</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="P75" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q75">
+        <v>19</v>
+      </c>
+      <c r="R75">
+        <v>5</v>
+      </c>
+      <c r="S75">
+        <v>7</v>
+      </c>
+      <c r="T75">
+        <v>2</v>
+      </c>
+      <c r="U75">
+        <v>4</v>
+      </c>
+      <c r="V75">
+        <v>13</v>
+      </c>
+      <c r="W75">
+        <v>6</v>
+      </c>
+      <c r="X75">
+        <v>2</v>
+      </c>
+      <c r="Y75">
+        <v>2</v>
+      </c>
+      <c r="Z75">
+        <v>3</v>
+      </c>
+      <c r="AA75">
+        <v>0</v>
+      </c>
+      <c r="AB75">
+        <v>0</v>
+      </c>
+      <c r="AC75">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="AD75">
+        <v>0.33</v>
+      </c>
+      <c r="AE75">
+        <v>1.75</v>
+      </c>
+      <c r="AF75">
+        <v>3.5</v>
+      </c>
+      <c r="AG75">
+        <v>5</v>
+      </c>
+      <c r="AH75">
+        <v>1.81</v>
+      </c>
+      <c r="AI75">
+        <v>3.65</v>
+      </c>
+      <c r="AJ75">
+        <v>5.6</v>
+      </c>
+      <c r="AK75">
+        <v>1.8</v>
+      </c>
+      <c r="AL75">
+        <v>3.56</v>
+      </c>
+      <c r="AM75">
+        <v>5.2</v>
+      </c>
+      <c r="AN75">
+        <v>1.75</v>
+      </c>
+      <c r="AO75">
+        <v>3.47</v>
+      </c>
+      <c r="AP75">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="76" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>266</v>
+      </c>
+      <c r="B76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C76" t="s">
+        <v>134</v>
+      </c>
+      <c r="D76" s="1">
+        <v>46202</v>
+      </c>
+      <c r="E76" s="7">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>3</v>
+      </c>
+      <c r="O76">
+        <v>4</v>
+      </c>
+      <c r="P76" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q76">
+        <v>21</v>
+      </c>
+      <c r="R76">
+        <v>7</v>
+      </c>
+      <c r="S76">
+        <v>6</v>
+      </c>
+      <c r="T76">
+        <v>3</v>
+      </c>
+      <c r="U76">
+        <v>18</v>
+      </c>
+      <c r="V76">
+        <v>12</v>
+      </c>
+      <c r="W76">
+        <v>16</v>
+      </c>
+      <c r="X76">
+        <v>6</v>
+      </c>
+      <c r="Y76">
+        <v>2</v>
+      </c>
+      <c r="Z76">
+        <v>2</v>
+      </c>
+      <c r="AA76">
+        <v>0</v>
+      </c>
+      <c r="AB76">
+        <v>0</v>
+      </c>
+      <c r="AC76">
+        <v>1.57</v>
+      </c>
+      <c r="AD76">
+        <v>0.35</v>
+      </c>
+      <c r="AE76">
+        <v>1.33</v>
+      </c>
+      <c r="AF76">
+        <v>5</v>
+      </c>
+      <c r="AG76">
+        <v>9.5</v>
+      </c>
+      <c r="AH76">
+        <v>1.37</v>
+      </c>
+      <c r="AI76">
+        <v>5.3</v>
+      </c>
+      <c r="AJ76">
+        <v>12</v>
+      </c>
+      <c r="AK76">
+        <v>1.37</v>
+      </c>
+      <c r="AL76">
+        <v>5.3</v>
+      </c>
+      <c r="AM76">
+        <v>10</v>
+      </c>
+      <c r="AN76">
+        <v>1.33</v>
+      </c>
+      <c r="AO76">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="AP76">
+        <v>9.16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>266</v>
+      </c>
+      <c r="B77" t="s">
+        <v>50</v>
+      </c>
+      <c r="C77" t="s">
+        <v>76</v>
+      </c>
+      <c r="D77" s="1">
+        <v>46203</v>
+      </c>
+      <c r="E77" s="7">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77">
+        <v>1</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>2</v>
+      </c>
+      <c r="O77">
+        <v>3</v>
+      </c>
+      <c r="P77" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q77">
+        <v>6</v>
+      </c>
+      <c r="R77">
+        <v>11</v>
+      </c>
+      <c r="S77">
+        <v>2</v>
+      </c>
+      <c r="T77">
+        <v>5</v>
+      </c>
+      <c r="U77">
+        <v>18</v>
+      </c>
+      <c r="V77">
+        <v>15</v>
+      </c>
+      <c r="W77">
+        <v>5</v>
+      </c>
+      <c r="X77">
+        <v>8</v>
+      </c>
+      <c r="Y77">
+        <v>0</v>
+      </c>
+      <c r="Z77">
+        <v>1</v>
+      </c>
+      <c r="AA77">
+        <v>0</v>
+      </c>
+      <c r="AB77">
+        <v>0</v>
+      </c>
+      <c r="AC77">
+        <v>0.24</v>
+      </c>
+      <c r="AD77">
+        <v>1.38</v>
+      </c>
+      <c r="AE77">
+        <v>2.35</v>
+      </c>
+      <c r="AF77">
+        <v>3.1</v>
+      </c>
+      <c r="AG77">
+        <v>3.3</v>
+      </c>
+      <c r="AH77">
+        <v>2.48</v>
+      </c>
+      <c r="AI77">
+        <v>3.1</v>
+      </c>
+      <c r="AJ77">
+        <v>3.55</v>
+      </c>
+      <c r="AK77">
+        <v>2.44</v>
+      </c>
+      <c r="AL77">
+        <v>3.1</v>
+      </c>
+      <c r="AM77">
+        <v>3.35</v>
+      </c>
+      <c r="AN77">
+        <v>2.34</v>
+      </c>
+      <c r="AO77">
+        <v>3.05</v>
+      </c>
+      <c r="AP77">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>266</v>
+      </c>
+      <c r="B78" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" t="s">
+        <v>56</v>
+      </c>
+      <c r="D78" s="1">
+        <v>46203</v>
+      </c>
+      <c r="E78" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78">
+        <v>2</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78">
+        <v>1</v>
+      </c>
+      <c r="P78" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q78">
+        <v>14</v>
+      </c>
+      <c r="R78">
+        <v>9</v>
+      </c>
+      <c r="S78">
+        <v>5</v>
+      </c>
+      <c r="T78">
+        <v>4</v>
+      </c>
+      <c r="U78">
+        <v>6</v>
+      </c>
+      <c r="V78">
+        <v>7</v>
+      </c>
+      <c r="W78">
+        <v>14</v>
+      </c>
+      <c r="X78">
+        <v>3</v>
+      </c>
+      <c r="Y78">
+        <v>0</v>
+      </c>
+      <c r="Z78">
+        <v>1</v>
+      </c>
+      <c r="AA78">
+        <v>0</v>
+      </c>
+      <c r="AB78">
+        <v>0</v>
+      </c>
+      <c r="AC78">
+        <v>1.49</v>
+      </c>
+      <c r="AD78">
+        <v>1.91</v>
+      </c>
+      <c r="AE78">
+        <v>3.7</v>
+      </c>
+      <c r="AF78">
+        <v>3.3</v>
+      </c>
+      <c r="AG78">
+        <v>2.1</v>
+      </c>
+      <c r="AH78">
+        <v>3.85</v>
+      </c>
+      <c r="AI78">
+        <v>3.4</v>
+      </c>
+      <c r="AJ78">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AK78">
+        <v>3.7</v>
+      </c>
+      <c r="AL78">
+        <v>3.4</v>
+      </c>
+      <c r="AM78">
+        <v>2.15</v>
+      </c>
+      <c r="AN78">
+        <v>3.52</v>
+      </c>
+      <c r="AO78">
+        <v>3.29</v>
+      </c>
+      <c r="AP78">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>266</v>
+      </c>
+      <c r="B79" t="s">
+        <v>60</v>
+      </c>
+      <c r="C79" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="1">
+        <v>46203</v>
+      </c>
+      <c r="E79" s="7">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F79">
+        <v>3</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="P79" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q79">
+        <v>25</v>
+      </c>
+      <c r="R79">
+        <v>8</v>
+      </c>
+      <c r="S79">
+        <v>12</v>
+      </c>
+      <c r="T79">
+        <v>3</v>
+      </c>
+      <c r="U79">
+        <v>14</v>
+      </c>
+      <c r="V79">
+        <v>10</v>
+      </c>
+      <c r="W79">
+        <v>9</v>
+      </c>
+      <c r="X79">
+        <v>1</v>
+      </c>
+      <c r="Y79">
+        <v>0</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+      <c r="AA79">
+        <v>0</v>
+      </c>
+      <c r="AB79">
+        <v>0</v>
+      </c>
+      <c r="AC79">
+        <v>3.24</v>
+      </c>
+      <c r="AD79">
+        <v>0.7</v>
+      </c>
+      <c r="AE79">
+        <v>1.29</v>
+      </c>
+      <c r="AF79">
+        <v>5.75</v>
+      </c>
+      <c r="AG79">
+        <v>10</v>
+      </c>
+      <c r="AH79">
+        <v>1.3</v>
+      </c>
+      <c r="AI79">
+        <v>6.2</v>
+      </c>
+      <c r="AJ79">
+        <v>12.5</v>
+      </c>
+      <c r="AK79">
+        <v>1.32</v>
+      </c>
+      <c r="AL79">
+        <v>6.2</v>
+      </c>
+      <c r="AM79">
+        <v>11</v>
+      </c>
+      <c r="AN79">
+        <v>1.28</v>
+      </c>
+      <c r="AO79">
+        <v>5.82</v>
+      </c>
+      <c r="AP79">
+        <v>9.4700000000000006</v>
+      </c>
+    </row>
+    <row r="80" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>266</v>
+      </c>
+      <c r="B80" t="s">
+        <v>253</v>
+      </c>
+      <c r="C80" t="s">
+        <v>135</v>
+      </c>
+      <c r="D80" s="1">
+        <v>46204</v>
+      </c>
+      <c r="E80" s="7">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F80">
+        <v>2</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="P80" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q80">
+        <v>15</v>
+      </c>
+      <c r="R80">
+        <v>7</v>
+      </c>
+      <c r="S80">
+        <v>3</v>
+      </c>
+      <c r="T80">
+        <v>1</v>
+      </c>
+      <c r="U80">
+        <v>10</v>
+      </c>
+      <c r="V80">
+        <v>14</v>
+      </c>
+      <c r="W80">
+        <v>3</v>
+      </c>
+      <c r="X80">
+        <v>8</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
+      </c>
+      <c r="Z80">
+        <v>3</v>
+      </c>
+      <c r="AA80">
+        <v>0</v>
+      </c>
+      <c r="AB80">
+        <v>1</v>
+      </c>
+      <c r="AC80">
+        <v>1.05</v>
+      </c>
+      <c r="AD80">
+        <v>0.75</v>
+      </c>
+      <c r="AE80">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AF80">
+        <v>2.7</v>
+      </c>
+      <c r="AG80">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AH80">
+        <v>2.34</v>
+      </c>
+      <c r="AI80">
+        <v>2.84</v>
+      </c>
+      <c r="AJ80">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AK80">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="AL80">
+        <v>2.83</v>
+      </c>
+      <c r="AM80">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AN80">
+        <v>2.25</v>
+      </c>
+      <c r="AO80">
+        <v>2.75</v>
+      </c>
+      <c r="AP80">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>266</v>
+      </c>
+      <c r="B81" t="s">
+        <v>58</v>
+      </c>
+      <c r="C81" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1">
+        <v>46204</v>
+      </c>
+      <c r="E81" s="7">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F81">
+        <v>2</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+      <c r="J81">
+        <v>2</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="P81" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q81">
+        <v>16</v>
+      </c>
+      <c r="R81">
+        <v>7</v>
+      </c>
+      <c r="S81">
+        <v>7</v>
+      </c>
+      <c r="T81">
+        <v>2</v>
+      </c>
+      <c r="U81">
+        <v>10</v>
+      </c>
+      <c r="V81">
+        <v>12</v>
+      </c>
+      <c r="W81">
+        <v>5</v>
+      </c>
+      <c r="X81">
+        <v>3</v>
+      </c>
+      <c r="Y81">
+        <v>1</v>
+      </c>
+      <c r="Z81">
+        <v>1</v>
+      </c>
+      <c r="AA81">
+        <v>0</v>
+      </c>
+      <c r="AB81">
+        <v>0</v>
+      </c>
+      <c r="AC81">
+        <v>2.15</v>
+      </c>
+      <c r="AD81">
+        <v>0.77</v>
+      </c>
+      <c r="AE81">
+        <v>1.29</v>
+      </c>
+      <c r="AF81">
+        <v>5.25</v>
+      </c>
+      <c r="AG81">
+        <v>13</v>
+      </c>
+      <c r="AH81">
+        <v>1.31</v>
+      </c>
+      <c r="AI81">
+        <v>5.4</v>
+      </c>
+      <c r="AJ81">
+        <v>17</v>
+      </c>
+      <c r="AK81">
+        <v>1.32</v>
+      </c>
+      <c r="AL81">
+        <v>5.25</v>
+      </c>
+      <c r="AM81">
+        <v>14</v>
+      </c>
+      <c r="AN81">
+        <v>1.28</v>
+      </c>
+      <c r="AO81">
+        <v>5.09</v>
+      </c>
+      <c r="AP81">
+        <v>12.09</v>
+      </c>
+    </row>
+    <row r="82" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>266</v>
+      </c>
+      <c r="B82" t="s">
+        <v>36</v>
+      </c>
+      <c r="C82" t="s">
+        <v>81</v>
+      </c>
+      <c r="D82" s="1">
+        <v>46204</v>
+      </c>
+      <c r="E82" s="7">
+        <v>0.875</v>
+      </c>
+      <c r="F82">
+        <v>2</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82">
+        <v>2</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="P82" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q82">
+        <v>19</v>
+      </c>
+      <c r="R82">
+        <v>19</v>
+      </c>
+      <c r="S82">
+        <v>5</v>
+      </c>
+      <c r="T82">
+        <v>5</v>
+      </c>
+      <c r="U82">
+        <v>22</v>
+      </c>
+      <c r="V82">
+        <v>12</v>
+      </c>
+      <c r="W82">
+        <v>4</v>
+      </c>
+      <c r="X82">
+        <v>2</v>
+      </c>
+      <c r="Y82">
+        <v>1</v>
+      </c>
+      <c r="Z82">
+        <v>1</v>
+      </c>
+      <c r="AA82">
+        <v>0</v>
+      </c>
+      <c r="AB82">
+        <v>0</v>
+      </c>
+      <c r="AC82">
+        <v>1.75</v>
+      </c>
+      <c r="AD82">
+        <v>3.58</v>
+      </c>
+      <c r="AE82">
+        <v>1.91</v>
+      </c>
+      <c r="AF82">
+        <v>3.4</v>
+      </c>
+      <c r="AG82">
+        <v>4.2</v>
+      </c>
+      <c r="AH82">
+        <v>2</v>
+      </c>
+      <c r="AI82">
+        <v>3.55</v>
+      </c>
+      <c r="AJ82">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AK82">
+        <v>2</v>
+      </c>
+      <c r="AL82">
+        <v>3.55</v>
+      </c>
+      <c r="AM82">
+        <v>4.25</v>
+      </c>
+      <c r="AN82">
+        <v>1.92</v>
+      </c>
+      <c r="AO82">
+        <v>3.39</v>
+      </c>
+      <c r="AP82">
+        <v>4.0199999999999996</v>
+      </c>
+    </row>
+    <row r="83" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>266</v>
+      </c>
+      <c r="B83" t="s">
+        <v>257</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" s="1">
+        <v>46205</v>
+      </c>
+      <c r="E83" s="7">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="P83" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q83">
+        <v>8</v>
+      </c>
+      <c r="R83">
+        <v>10</v>
+      </c>
+      <c r="S83">
+        <v>2</v>
+      </c>
+      <c r="T83">
+        <v>3</v>
+      </c>
+      <c r="U83">
+        <v>7</v>
+      </c>
+      <c r="V83">
+        <v>13</v>
+      </c>
+      <c r="W83">
+        <v>4</v>
+      </c>
+      <c r="X83">
+        <v>3</v>
+      </c>
+      <c r="Y83">
+        <v>0</v>
+      </c>
+      <c r="Z83">
+        <v>1</v>
+      </c>
+      <c r="AA83">
+        <v>1</v>
+      </c>
+      <c r="AB83">
+        <v>0</v>
+      </c>
+      <c r="AC83">
+        <v>0.88</v>
+      </c>
+      <c r="AD83">
+        <v>0.25</v>
+      </c>
+      <c r="AE83">
+        <v>1.33</v>
+      </c>
+      <c r="AF83">
+        <v>5.25</v>
+      </c>
+      <c r="AG83">
+        <v>9</v>
+      </c>
+      <c r="AH83">
+        <v>1.39</v>
+      </c>
+      <c r="AI83">
+        <v>5.4</v>
+      </c>
+      <c r="AJ83">
+        <v>10</v>
+      </c>
+      <c r="AK83">
+        <v>1.37</v>
+      </c>
+      <c r="AL83">
+        <v>5.3</v>
+      </c>
+      <c r="AM83">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="AN83">
+        <v>1.34</v>
+      </c>
+      <c r="AO83">
+        <v>5.07</v>
+      </c>
+      <c r="AP83">
+        <v>8.44</v>
+      </c>
+    </row>
+    <row r="84" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>266</v>
+      </c>
+      <c r="B84" t="s">
+        <v>44</v>
+      </c>
+      <c r="C84" t="s">
+        <v>33</v>
+      </c>
+      <c r="D84" s="1">
+        <v>46205</v>
+      </c>
+      <c r="E84" s="7">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F84">
+        <v>3</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="P84" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q84">
+        <v>23</v>
+      </c>
+      <c r="R84">
+        <v>5</v>
+      </c>
+      <c r="S84">
+        <v>10</v>
+      </c>
+      <c r="T84">
+        <v>0</v>
+      </c>
+      <c r="U84">
+        <v>8</v>
+      </c>
+      <c r="V84">
+        <v>15</v>
+      </c>
+      <c r="W84">
+        <v>9</v>
+      </c>
+      <c r="X84">
+        <v>0</v>
+      </c>
+      <c r="Y84">
+        <v>0</v>
+      </c>
+      <c r="Z84">
+        <v>1</v>
+      </c>
+      <c r="AA84">
+        <v>0</v>
+      </c>
+      <c r="AB84">
+        <v>0</v>
+      </c>
+      <c r="AC84">
+        <v>2.8</v>
+      </c>
+      <c r="AD84">
+        <v>0.32</v>
+      </c>
+      <c r="AE84">
+        <v>1.33</v>
+      </c>
+      <c r="AF84">
+        <v>5</v>
+      </c>
+      <c r="AG84">
+        <v>10</v>
+      </c>
+      <c r="AH84">
+        <v>1.37</v>
+      </c>
+      <c r="AI84">
+        <v>5.3</v>
+      </c>
+      <c r="AJ84">
+        <v>11.5</v>
+      </c>
+      <c r="AK84">
+        <v>1.35</v>
+      </c>
+      <c r="AL84">
+        <v>5.25</v>
+      </c>
+      <c r="AM84">
+        <v>11.5</v>
+      </c>
+      <c r="AN84">
+        <v>1.33</v>
+      </c>
+      <c r="AO84">
+        <v>5.04</v>
+      </c>
+      <c r="AP84">
+        <v>9.5299999999999994</v>
+      </c>
+    </row>
+    <row r="85" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>266</v>
+      </c>
+      <c r="B85" t="s">
+        <v>64</v>
+      </c>
+      <c r="C85" t="s">
+        <v>47</v>
+      </c>
+      <c r="D85" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E85" s="7">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>2</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
+      </c>
+      <c r="P85" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q85">
+        <v>15</v>
+      </c>
+      <c r="R85">
+        <v>13</v>
+      </c>
+      <c r="S85">
+        <v>3</v>
+      </c>
+      <c r="T85">
+        <v>6</v>
+      </c>
+      <c r="U85">
+        <v>6</v>
+      </c>
+      <c r="V85">
+        <v>12</v>
+      </c>
+      <c r="W85">
+        <v>9</v>
+      </c>
+      <c r="X85">
+        <v>5</v>
+      </c>
+      <c r="Y85">
+        <v>1</v>
+      </c>
+      <c r="Z85">
+        <v>2</v>
+      </c>
+      <c r="AA85">
+        <v>0</v>
+      </c>
+      <c r="AB85">
+        <v>0</v>
+      </c>
+      <c r="AC85">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AD85">
+        <v>1.34</v>
+      </c>
+      <c r="AE85">
+        <v>1.7</v>
+      </c>
+      <c r="AF85">
+        <v>3.6</v>
+      </c>
+      <c r="AG85">
+        <v>5.5</v>
+      </c>
+      <c r="AH85">
+        <v>1.73</v>
+      </c>
+      <c r="AI85">
+        <v>3.8</v>
+      </c>
+      <c r="AJ85">
+        <v>6</v>
+      </c>
+      <c r="AK85">
+        <v>1.74</v>
+      </c>
+      <c r="AL85">
+        <v>3.75</v>
+      </c>
+      <c r="AM85">
+        <v>5.5</v>
+      </c>
+      <c r="AN85">
+        <v>1.67</v>
+      </c>
+      <c r="AO85">
+        <v>3.67</v>
+      </c>
+      <c r="AP85">
+        <v>5.23</v>
+      </c>
+    </row>
+    <row r="86" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>266</v>
+      </c>
+      <c r="B86" t="s">
+        <v>41</v>
+      </c>
+      <c r="C86" t="s">
+        <v>87</v>
+      </c>
+      <c r="D86" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E86" s="7">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F86">
+        <v>2</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="P86" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q86">
+        <v>11</v>
+      </c>
+      <c r="R86">
+        <v>8</v>
+      </c>
+      <c r="S86">
+        <v>5</v>
+      </c>
+      <c r="T86">
+        <v>2</v>
+      </c>
+      <c r="U86">
+        <v>10</v>
+      </c>
+      <c r="V86">
+        <v>12</v>
+      </c>
+      <c r="W86">
+        <v>4</v>
+      </c>
+      <c r="X86">
+        <v>2</v>
+      </c>
+      <c r="Y86">
+        <v>0</v>
+      </c>
+      <c r="Z86">
+        <v>2</v>
+      </c>
+      <c r="AA86">
+        <v>0</v>
+      </c>
+      <c r="AB86">
+        <v>0</v>
+      </c>
+      <c r="AC86">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="AD86">
+        <v>0.74</v>
+      </c>
+      <c r="AE86">
+        <v>1.95</v>
+      </c>
+      <c r="AF86">
+        <v>3.1</v>
+      </c>
+      <c r="AG86">
+        <v>4.5</v>
+      </c>
+      <c r="AH86">
+        <v>2.04</v>
+      </c>
+      <c r="AI86">
+        <v>3.3</v>
+      </c>
+      <c r="AJ86">
+        <v>4.7</v>
+      </c>
+      <c r="AK86">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AL86">
+        <v>3.3</v>
+      </c>
+      <c r="AM86">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AN86">
+        <v>1.95</v>
+      </c>
+      <c r="AO86">
+        <v>3.18</v>
+      </c>
+      <c r="AP86">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>266</v>
+      </c>
+      <c r="B87" t="s">
+        <v>149</v>
+      </c>
+      <c r="C87" t="s">
+        <v>117</v>
+      </c>
+      <c r="D87" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E87" s="7">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <v>1</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>2</v>
+      </c>
+      <c r="O87">
+        <v>4</v>
+      </c>
+      <c r="P87" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q87">
+        <v>16</v>
+      </c>
+      <c r="R87">
+        <v>14</v>
+      </c>
+      <c r="S87">
+        <v>1</v>
+      </c>
+      <c r="T87">
+        <v>3</v>
+      </c>
+      <c r="U87">
+        <v>12</v>
+      </c>
+      <c r="V87">
+        <v>14</v>
+      </c>
+      <c r="W87">
+        <v>4</v>
+      </c>
+      <c r="X87">
+        <v>7</v>
+      </c>
+      <c r="Y87">
+        <v>0</v>
+      </c>
+      <c r="Z87">
+        <v>2</v>
+      </c>
+      <c r="AA87">
+        <v>0</v>
+      </c>
+      <c r="AB87">
+        <v>0</v>
+      </c>
+      <c r="AC87">
+        <v>0.84</v>
+      </c>
+      <c r="AD87">
+        <v>1.33</v>
+      </c>
+      <c r="AE87">
+        <v>3.6</v>
+      </c>
+      <c r="AF87">
+        <v>2.88</v>
+      </c>
+      <c r="AG87">
+        <v>2.35</v>
+      </c>
+      <c r="AH87">
+        <v>3.85</v>
+      </c>
+      <c r="AI87">
+        <v>2.92</v>
+      </c>
+      <c r="AJ87">
+        <v>2.48</v>
+      </c>
+      <c r="AK87">
+        <v>3.74</v>
+      </c>
+      <c r="AL87">
+        <v>2.9</v>
+      </c>
+      <c r="AM87">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="AN87">
+        <v>3.5</v>
+      </c>
+      <c r="AO87">
+        <v>2.81</v>
+      </c>
+      <c r="AP87">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="88" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>266</v>
+      </c>
+      <c r="B88" t="s">
+        <v>136</v>
+      </c>
+      <c r="C88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D88" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E88" s="7">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
+      </c>
+      <c r="L88">
+        <v>2</v>
+      </c>
+      <c r="M88">
+        <v>1</v>
+      </c>
+      <c r="P88" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q88">
+        <v>22</v>
+      </c>
+      <c r="R88">
+        <v>16</v>
+      </c>
+      <c r="S88">
+        <v>10</v>
+      </c>
+      <c r="T88">
+        <v>5</v>
+      </c>
+      <c r="U88">
+        <v>13</v>
+      </c>
+      <c r="V88">
+        <v>12</v>
+      </c>
+      <c r="W88">
+        <v>8</v>
+      </c>
+      <c r="X88">
+        <v>8</v>
+      </c>
+      <c r="Y88">
+        <v>1</v>
+      </c>
+      <c r="Z88">
+        <v>1</v>
+      </c>
+      <c r="AA88">
+        <v>0</v>
+      </c>
+      <c r="AB88">
+        <v>0</v>
+      </c>
+      <c r="AC88">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="AD88">
+        <v>0.47</v>
+      </c>
+      <c r="AE88">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="AF88">
+        <v>8</v>
+      </c>
+      <c r="AG88">
+        <v>19</v>
+      </c>
+      <c r="AH88">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AI88">
+        <v>9.6</v>
+      </c>
+      <c r="AJ88">
+        <v>30</v>
+      </c>
+      <c r="AK88">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AL88">
+        <v>9.5</v>
+      </c>
+      <c r="AM88">
+        <v>23.5</v>
+      </c>
+      <c r="AN88">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="AO88">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="AP88">
+        <v>20.16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>266</v>
+      </c>
+      <c r="B89" t="s">
+        <v>132</v>
+      </c>
+      <c r="C89" t="s">
+        <v>113</v>
+      </c>
+      <c r="D89" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E89" s="7">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="P89" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q89">
+        <v>20</v>
+      </c>
+      <c r="R89">
+        <v>8</v>
+      </c>
+      <c r="S89">
+        <v>8</v>
+      </c>
+      <c r="T89">
+        <v>0</v>
+      </c>
+      <c r="U89">
+        <v>14</v>
+      </c>
+      <c r="V89">
+        <v>10</v>
+      </c>
+      <c r="W89">
+        <v>3</v>
+      </c>
+      <c r="X89">
+        <v>2</v>
+      </c>
+      <c r="Y89">
+        <v>2</v>
+      </c>
+      <c r="Z89">
+        <v>3</v>
+      </c>
+      <c r="AA89">
+        <v>0</v>
+      </c>
+      <c r="AB89">
+        <v>0</v>
+      </c>
+      <c r="AC89">
+        <v>2.04</v>
+      </c>
+      <c r="AD89">
+        <v>0.27</v>
+      </c>
+      <c r="AE89">
+        <v>1.45</v>
+      </c>
+      <c r="AF89">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AG89">
+        <v>8.5</v>
+      </c>
+      <c r="AH89">
+        <v>1.47</v>
+      </c>
+      <c r="AI89">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AJ89">
+        <v>10</v>
+      </c>
+      <c r="AK89">
+        <v>1.48</v>
+      </c>
+      <c r="AL89">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AM89">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="AN89">
+        <v>1.42</v>
+      </c>
+      <c r="AO89">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="AP89">
+        <v>8.1300000000000008</v>
+      </c>
+    </row>
+    <row r="90" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>266</v>
+      </c>
+      <c r="B90" t="s">
+        <v>258</v>
+      </c>
+      <c r="C90" t="s">
+        <v>76</v>
+      </c>
+      <c r="D90" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E90" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>3</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>3</v>
+      </c>
+      <c r="P90" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q90">
+        <v>10</v>
+      </c>
+      <c r="R90">
+        <v>5</v>
+      </c>
+      <c r="S90">
+        <v>3</v>
+      </c>
+      <c r="T90">
+        <v>4</v>
+      </c>
+      <c r="U90">
+        <v>24</v>
+      </c>
+      <c r="V90">
+        <v>14</v>
+      </c>
+      <c r="W90">
+        <v>11</v>
+      </c>
+      <c r="X90">
+        <v>1</v>
+      </c>
+      <c r="Y90">
+        <v>4</v>
+      </c>
+      <c r="Z90">
+        <v>4</v>
+      </c>
+      <c r="AA90">
+        <v>0</v>
+      </c>
+      <c r="AB90">
+        <v>0</v>
+      </c>
+      <c r="AC90">
+        <v>0.84</v>
+      </c>
+      <c r="AD90">
+        <v>0.82</v>
+      </c>
+      <c r="AE90">
+        <v>5</v>
+      </c>
+      <c r="AF90">
+        <v>3.25</v>
+      </c>
+      <c r="AG90">
+        <v>1.83</v>
+      </c>
+      <c r="AH90">
+        <v>5.6</v>
+      </c>
+      <c r="AI90">
+        <v>3.35</v>
+      </c>
+      <c r="AJ90">
+        <v>1.89</v>
+      </c>
+      <c r="AK90">
+        <v>5.25</v>
+      </c>
+      <c r="AL90">
+        <v>3.4</v>
+      </c>
+      <c r="AM90">
+        <v>1.89</v>
+      </c>
+      <c r="AN90">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="AO90">
+        <v>3.26</v>
+      </c>
+      <c r="AP90">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="91" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>266</v>
+      </c>
+      <c r="B91" t="s">
+        <v>134</v>
+      </c>
+      <c r="C91" t="s">
+        <v>60</v>
+      </c>
+      <c r="D91" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E91" s="7">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
+      </c>
+      <c r="P91" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q91">
+        <v>5</v>
+      </c>
+      <c r="R91">
+        <v>15</v>
+      </c>
+      <c r="S91">
+        <v>0</v>
+      </c>
+      <c r="T91">
+        <v>5</v>
+      </c>
+      <c r="U91">
+        <v>13</v>
+      </c>
+      <c r="V91">
+        <v>11</v>
+      </c>
+      <c r="W91">
+        <v>2</v>
+      </c>
+      <c r="X91">
+        <v>12</v>
+      </c>
+      <c r="Y91">
+        <v>0</v>
+      </c>
+      <c r="Z91">
+        <v>3</v>
+      </c>
+      <c r="AA91">
+        <v>0</v>
+      </c>
+      <c r="AB91">
+        <v>0</v>
+      </c>
+      <c r="AC91">
+        <v>0.13</v>
+      </c>
+      <c r="AD91">
+        <v>1.46</v>
+      </c>
+      <c r="AE91">
+        <v>17</v>
+      </c>
+      <c r="AF91">
+        <v>6.5</v>
+      </c>
+      <c r="AG91">
+        <v>1.18</v>
+      </c>
+      <c r="AH91">
+        <v>22</v>
+      </c>
+      <c r="AI91">
+        <v>7</v>
+      </c>
+      <c r="AJ91">
+        <v>1.22</v>
+      </c>
+      <c r="AK91">
+        <v>18</v>
+      </c>
+      <c r="AL91">
+        <v>6.75</v>
+      </c>
+      <c r="AM91">
+        <v>1.22</v>
+      </c>
+      <c r="AN91">
+        <v>14.94</v>
+      </c>
+      <c r="AO91">
+        <v>6.37</v>
+      </c>
+      <c r="AP91">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>266</v>
+      </c>
+      <c r="B92" t="s">
+        <v>128</v>
+      </c>
+      <c r="C92" t="s">
+        <v>56</v>
+      </c>
+      <c r="D92" s="1">
+        <v>46208</v>
+      </c>
+      <c r="E92" s="7">
+        <v>0.875</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92">
+        <v>2</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92">
+        <v>2</v>
+      </c>
+      <c r="P92" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q92">
+        <v>14</v>
+      </c>
+      <c r="R92">
+        <v>9</v>
+      </c>
+      <c r="S92">
+        <v>4</v>
+      </c>
+      <c r="T92">
+        <v>5</v>
+      </c>
+      <c r="U92">
+        <v>7</v>
+      </c>
+      <c r="V92">
+        <v>6</v>
+      </c>
+      <c r="W92">
+        <v>5</v>
+      </c>
+      <c r="X92">
+        <v>5</v>
+      </c>
+      <c r="Y92">
+        <v>1</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+      <c r="AA92">
+        <v>0</v>
+      </c>
+      <c r="AB92">
+        <v>0</v>
+      </c>
+      <c r="AC92">
+        <v>2.62</v>
+      </c>
+      <c r="AD92">
+        <v>1.06</v>
+      </c>
+      <c r="AE92">
+        <v>1.75</v>
+      </c>
+      <c r="AF92">
+        <v>3.6</v>
+      </c>
+      <c r="AG92">
+        <v>4.75</v>
+      </c>
+      <c r="AH92">
+        <v>1.82</v>
+      </c>
+      <c r="AI92">
+        <v>3.85</v>
+      </c>
+      <c r="AJ92">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AK92">
+        <v>1.8</v>
+      </c>
+      <c r="AL92">
+        <v>3.9</v>
+      </c>
+      <c r="AM92">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="AN92">
+        <v>1.75</v>
+      </c>
+      <c r="AO92">
+        <v>3.68</v>
+      </c>
+      <c r="AP92">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="93" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>266</v>
+      </c>
+      <c r="B93" t="s">
+        <v>253</v>
+      </c>
+      <c r="C93" t="s">
+        <v>58</v>
+      </c>
+      <c r="D93" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E93" s="7">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F93">
+        <v>2</v>
+      </c>
+      <c r="G93">
+        <v>3</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93">
+        <v>2</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+      <c r="K93">
+        <v>1</v>
+      </c>
+      <c r="P93" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q93">
+        <v>20</v>
+      </c>
+      <c r="R93">
+        <v>6</v>
+      </c>
+      <c r="S93">
+        <v>5</v>
+      </c>
+      <c r="T93">
+        <v>5</v>
+      </c>
+      <c r="U93">
+        <v>14</v>
+      </c>
+      <c r="V93">
+        <v>7</v>
+      </c>
+      <c r="W93">
+        <v>12</v>
+      </c>
+      <c r="X93">
+        <v>2</v>
+      </c>
+      <c r="Y93">
+        <v>2</v>
+      </c>
+      <c r="Z93">
+        <v>4</v>
+      </c>
+      <c r="AA93">
+        <v>0</v>
+      </c>
+      <c r="AB93">
+        <v>1</v>
+      </c>
+      <c r="AC93">
+        <v>1.88</v>
+      </c>
+      <c r="AD93">
+        <v>1.61</v>
+      </c>
+      <c r="AE93">
+        <v>3</v>
+      </c>
+      <c r="AF93">
+        <v>3</v>
+      </c>
+      <c r="AG93">
+        <v>2.6</v>
+      </c>
+      <c r="AH93">
+        <v>3.15</v>
+      </c>
+      <c r="AI93">
+        <v>3.15</v>
+      </c>
+      <c r="AJ93">
+        <v>2.68</v>
+      </c>
+      <c r="AK93">
+        <v>3.1</v>
+      </c>
+      <c r="AL93">
+        <v>3.15</v>
+      </c>
+      <c r="AM93">
+        <v>2.62</v>
+      </c>
+      <c r="AN93">
+        <v>2.98</v>
+      </c>
+      <c r="AO93">
+        <v>3</v>
+      </c>
+      <c r="AP93">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="94" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>266</v>
+      </c>
+      <c r="B94" t="s">
+        <v>64</v>
+      </c>
+      <c r="C94" t="s">
+        <v>44</v>
+      </c>
+      <c r="D94" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E94" s="7">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>1</v>
+      </c>
+      <c r="P94" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q94">
+        <v>10</v>
+      </c>
+      <c r="R94">
+        <v>15</v>
+      </c>
+      <c r="S94">
+        <v>2</v>
+      </c>
+      <c r="T94">
+        <v>6</v>
+      </c>
+      <c r="U94">
+        <v>9</v>
+      </c>
+      <c r="V94">
+        <v>13</v>
+      </c>
+      <c r="W94">
+        <v>3</v>
+      </c>
+      <c r="X94">
+        <v>7</v>
+      </c>
+      <c r="Y94">
+        <v>2</v>
+      </c>
+      <c r="Z94">
+        <v>1</v>
+      </c>
+      <c r="AA94">
+        <v>0</v>
+      </c>
+      <c r="AB94">
+        <v>0</v>
+      </c>
+      <c r="AC94">
+        <v>0.63</v>
+      </c>
+      <c r="AD94">
+        <v>1.68</v>
+      </c>
+      <c r="AE94">
+        <v>3.9</v>
+      </c>
+      <c r="AF94">
+        <v>3.5</v>
+      </c>
+      <c r="AG94">
+        <v>1.95</v>
+      </c>
+      <c r="AH94">
+        <v>4.2</v>
+      </c>
+      <c r="AI94">
+        <v>3.6</v>
+      </c>
+      <c r="AJ94">
+        <v>2.04</v>
+      </c>
+      <c r="AK94">
+        <v>3.9</v>
+      </c>
+      <c r="AL94">
+        <v>3.6</v>
+      </c>
+      <c r="AM94">
+        <v>2</v>
+      </c>
+      <c r="AN94">
+        <v>3.78</v>
+      </c>
+      <c r="AO94">
+        <v>3.47</v>
+      </c>
+      <c r="AP94">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="95" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>266</v>
+      </c>
+      <c r="B95" t="s">
+        <v>257</v>
+      </c>
+      <c r="C95" t="s">
+        <v>36</v>
+      </c>
+      <c r="D95" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E95" s="7">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95">
+        <v>4</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95">
+        <v>2</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>2</v>
+      </c>
+      <c r="P95" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q95">
+        <v>7</v>
+      </c>
+      <c r="R95">
+        <v>15</v>
+      </c>
+      <c r="S95">
+        <v>2</v>
+      </c>
+      <c r="T95">
+        <v>7</v>
+      </c>
+      <c r="U95">
+        <v>11</v>
+      </c>
+      <c r="V95">
+        <v>9</v>
+      </c>
+      <c r="W95">
+        <v>3</v>
+      </c>
+      <c r="X95">
+        <v>5</v>
+      </c>
+      <c r="Y95">
+        <v>2</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+      <c r="AA95">
+        <v>0</v>
+      </c>
+      <c r="AB95">
+        <v>0</v>
+      </c>
+      <c r="AC95">
+        <v>0.63</v>
+      </c>
+      <c r="AD95">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="AE95">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AF95">
+        <v>3.2</v>
+      </c>
+      <c r="AG95">
+        <v>2.9</v>
+      </c>
+      <c r="AH95">
+        <v>2.7</v>
+      </c>
+      <c r="AI95">
+        <v>3.3</v>
+      </c>
+      <c r="AJ95">
+        <v>3</v>
+      </c>
+      <c r="AK95">
+        <v>2.6</v>
+      </c>
+      <c r="AL95">
+        <v>3.4</v>
+      </c>
+      <c r="AM95">
+        <v>2.94</v>
+      </c>
+      <c r="AN95">
+        <v>2.52</v>
+      </c>
+      <c r="AO95">
+        <v>3.19</v>
+      </c>
+      <c r="AP95">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="96" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>266</v>
+      </c>
+      <c r="B96" t="s">
+        <v>136</v>
+      </c>
+      <c r="C96" t="s">
+        <v>117</v>
+      </c>
+      <c r="D96" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E96" s="7">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F96">
+        <v>3</v>
+      </c>
+      <c r="G96">
+        <v>2</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96">
+        <v>3</v>
+      </c>
+      <c r="K96">
+        <v>1</v>
+      </c>
+      <c r="P96" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q96">
+        <v>19</v>
+      </c>
+      <c r="R96">
+        <v>5</v>
+      </c>
+      <c r="S96">
+        <v>7</v>
+      </c>
+      <c r="T96">
+        <v>2</v>
+      </c>
+      <c r="U96">
+        <v>13</v>
+      </c>
+      <c r="V96">
+        <v>11</v>
+      </c>
+      <c r="W96">
+        <v>6</v>
+      </c>
+      <c r="X96">
+        <v>1</v>
+      </c>
+      <c r="Y96">
+        <v>0</v>
+      </c>
+      <c r="Z96">
+        <v>4</v>
+      </c>
+      <c r="AA96">
+        <v>0</v>
+      </c>
+      <c r="AB96">
+        <v>0</v>
+      </c>
+      <c r="AC96">
+        <v>2.84</v>
+      </c>
+      <c r="AD96">
+        <v>0.89</v>
+      </c>
+      <c r="AE96">
+        <v>1.33</v>
+      </c>
+      <c r="AF96">
+        <v>4.75</v>
+      </c>
+      <c r="AG96">
+        <v>11</v>
+      </c>
+      <c r="AH96">
+        <v>1.37</v>
+      </c>
+      <c r="AI96">
+        <v>5</v>
+      </c>
+      <c r="AJ96">
+        <v>13.5</v>
+      </c>
+      <c r="AK96">
+        <v>1.35</v>
+      </c>
+      <c r="AL96">
+        <v>5</v>
+      </c>
+      <c r="AM96">
+        <v>12</v>
+      </c>
+      <c r="AN96">
+        <v>1.32</v>
+      </c>
+      <c r="AO96">
+        <v>4.72</v>
+      </c>
+      <c r="AP96">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>266</v>
+      </c>
+      <c r="B97" t="s">
+        <v>41</v>
+      </c>
+      <c r="C97" t="s">
+        <v>132</v>
+      </c>
+      <c r="D97" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E97" s="7">
+        <v>0.875</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>4</v>
+      </c>
+      <c r="O97">
+        <v>3</v>
+      </c>
+      <c r="P97" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q97">
+        <v>7</v>
+      </c>
+      <c r="R97">
+        <v>15</v>
+      </c>
+      <c r="S97">
+        <v>2</v>
+      </c>
+      <c r="T97">
+        <v>3</v>
+      </c>
+      <c r="U97">
+        <v>22</v>
+      </c>
+      <c r="V97">
+        <v>21</v>
+      </c>
+      <c r="W97">
+        <v>3</v>
+      </c>
+      <c r="X97">
+        <v>7</v>
+      </c>
+      <c r="Y97">
+        <v>3</v>
+      </c>
+      <c r="Z97">
+        <v>2</v>
+      </c>
+      <c r="AA97">
+        <v>0</v>
+      </c>
+      <c r="AB97">
+        <v>0</v>
+      </c>
+      <c r="AC97">
+        <v>0.38</v>
+      </c>
+      <c r="AD97">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="AE97">
+        <v>3.6</v>
+      </c>
+      <c r="AF97">
+        <v>2.88</v>
+      </c>
+      <c r="AG97">
+        <v>2.35</v>
+      </c>
+      <c r="AH97">
+        <v>3.8</v>
+      </c>
+      <c r="AI97">
+        <v>2.98</v>
+      </c>
+      <c r="AJ97">
+        <v>2.46</v>
+      </c>
+      <c r="AK97">
+        <v>3.7</v>
+      </c>
+      <c r="AL97">
+        <v>3</v>
+      </c>
+      <c r="AM97">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="AN97">
+        <v>3.48</v>
+      </c>
+      <c r="AO97">
+        <v>2.86</v>
+      </c>
+      <c r="AP97">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="98" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>266</v>
+      </c>
+      <c r="B98" t="s">
+        <v>60</v>
+      </c>
+      <c r="C98" t="s">
+        <v>76</v>
+      </c>
+      <c r="D98" s="1">
+        <v>46212</v>
+      </c>
+      <c r="E98" s="7">
+        <v>0.875</v>
+      </c>
+      <c r="F98">
+        <v>2</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="P98" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q98">
+        <v>22</v>
+      </c>
+      <c r="R98">
+        <v>5</v>
+      </c>
+      <c r="S98">
+        <v>8</v>
+      </c>
+      <c r="T98">
+        <v>1</v>
+      </c>
+      <c r="U98">
+        <v>10</v>
+      </c>
+      <c r="V98">
+        <v>13</v>
+      </c>
+      <c r="W98">
+        <v>5</v>
+      </c>
+      <c r="X98">
+        <v>5</v>
+      </c>
+      <c r="Y98">
+        <v>0</v>
+      </c>
+      <c r="Z98">
+        <v>1</v>
+      </c>
+      <c r="AA98">
+        <v>0</v>
+      </c>
+      <c r="AB98">
+        <v>0</v>
+      </c>
+      <c r="AC98">
+        <v>3.68</v>
+      </c>
+      <c r="AD98">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AE98">
+        <v>1.57</v>
+      </c>
+      <c r="AF98">
+        <v>3.8</v>
+      </c>
+      <c r="AG98">
+        <v>6.5</v>
+      </c>
+      <c r="AH98">
+        <v>1.61</v>
+      </c>
+      <c r="AI98">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AJ98">
+        <v>7</v>
+      </c>
+      <c r="AK98">
+        <v>1.6</v>
+      </c>
+      <c r="AL98">
+        <v>4</v>
+      </c>
+      <c r="AM98">
+        <v>6.6</v>
+      </c>
+      <c r="AN98">
+        <v>1.56</v>
+      </c>
+      <c r="AO98">
+        <v>3.88</v>
+      </c>
+      <c r="AP98">
+        <v>6.23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>266</v>
+      </c>
+      <c r="B99" t="s">
+        <v>44</v>
+      </c>
+      <c r="C99" t="s">
+        <v>36</v>
+      </c>
+      <c r="D99" s="1">
+        <v>46213</v>
+      </c>
+      <c r="E99" s="7">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F99">
+        <v>2</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="P99" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q99">
+        <v>17</v>
+      </c>
+      <c r="R99">
+        <v>5</v>
+      </c>
+      <c r="S99">
+        <v>8</v>
+      </c>
+      <c r="T99">
+        <v>2</v>
+      </c>
+      <c r="U99">
+        <v>13</v>
+      </c>
+      <c r="V99">
+        <v>18</v>
+      </c>
+      <c r="W99">
+        <v>5</v>
+      </c>
+      <c r="X99">
+        <v>1</v>
+      </c>
+      <c r="Y99">
+        <v>2</v>
+      </c>
+      <c r="Z99">
+        <v>2</v>
+      </c>
+      <c r="AA99">
+        <v>0</v>
+      </c>
+      <c r="AB99">
+        <v>0</v>
+      </c>
+      <c r="AC99">
+        <v>1.96</v>
+      </c>
+      <c r="AD99">
+        <v>0.35</v>
+      </c>
+      <c r="AE99">
+        <v>1.65</v>
+      </c>
+      <c r="AF99">
+        <v>3.8</v>
+      </c>
+      <c r="AG99">
+        <v>5.5</v>
+      </c>
+      <c r="AH99">
+        <v>1.69</v>
+      </c>
+      <c r="AI99">
+        <v>4</v>
+      </c>
+      <c r="AJ99">
+        <v>6</v>
+      </c>
+      <c r="AK99">
+        <v>1.67</v>
+      </c>
+      <c r="AL99">
+        <v>4</v>
+      </c>
+      <c r="AM99">
+        <v>5.5</v>
+      </c>
+      <c r="AN99">
+        <v>1.63</v>
+      </c>
+      <c r="AO99">
+        <v>3.86</v>
+      </c>
+      <c r="AP99">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>266</v>
+      </c>
+      <c r="B100" t="s">
+        <v>56</v>
+      </c>
+      <c r="C100" t="s">
+        <v>58</v>
+      </c>
+      <c r="D100" s="1">
+        <v>46214</v>
+      </c>
+      <c r="E100" s="7">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>1</v>
+      </c>
+      <c r="P100" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q100">
+        <v>13</v>
+      </c>
+      <c r="R100">
+        <v>14</v>
+      </c>
+      <c r="S100">
+        <v>4</v>
+      </c>
+      <c r="T100">
+        <v>8</v>
+      </c>
+      <c r="U100">
+        <v>10</v>
+      </c>
+      <c r="V100">
+        <v>8</v>
+      </c>
+      <c r="W100">
+        <v>7</v>
+      </c>
+      <c r="X100">
+        <v>4</v>
+      </c>
+      <c r="Y100">
+        <v>1</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+      <c r="AA100">
+        <v>0</v>
+      </c>
+      <c r="AB100">
+        <v>0</v>
+      </c>
+      <c r="AC100">
+        <v>0.68</v>
+      </c>
+      <c r="AD100">
+        <v>1.04</v>
+      </c>
+      <c r="AE100">
+        <v>4.2</v>
+      </c>
+      <c r="AF100">
+        <v>3.8</v>
+      </c>
+      <c r="AG100">
+        <v>1.8</v>
+      </c>
+      <c r="AH100">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AI100">
+        <v>4</v>
+      </c>
+      <c r="AJ100">
+        <v>1.86</v>
+      </c>
+      <c r="AK100">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AL100">
+        <v>3.95</v>
+      </c>
+      <c r="AM100">
+        <v>1.91</v>
+      </c>
+      <c r="AN100">
+        <v>4.05</v>
+      </c>
+      <c r="AO100">
+        <v>3.77</v>
+      </c>
+      <c r="AP100">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="101" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>266</v>
+      </c>
+      <c r="B101" t="s">
+        <v>136</v>
+      </c>
+      <c r="C101" t="s">
+        <v>41</v>
+      </c>
+      <c r="D101" s="1">
+        <v>46215</v>
+      </c>
+      <c r="E101" s="7">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
+      </c>
+      <c r="L101">
+        <v>2</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="P101" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q101">
+        <v>22</v>
+      </c>
+      <c r="R101">
+        <v>11</v>
+      </c>
+      <c r="S101">
+        <v>7</v>
+      </c>
+      <c r="T101">
+        <v>5</v>
+      </c>
+      <c r="U101">
+        <v>14</v>
+      </c>
+      <c r="V101">
+        <v>18</v>
+      </c>
+      <c r="W101">
+        <v>8</v>
+      </c>
+      <c r="X101">
+        <v>2</v>
+      </c>
+      <c r="Y101">
+        <v>3</v>
+      </c>
+      <c r="Z101">
+        <v>2</v>
+      </c>
+      <c r="AA101">
+        <v>0</v>
+      </c>
+      <c r="AB101">
+        <v>1</v>
+      </c>
+      <c r="AC101">
+        <v>1.94</v>
+      </c>
+      <c r="AD101">
+        <v>0.46</v>
+      </c>
+      <c r="AE101">
+        <v>1.7</v>
+      </c>
+      <c r="AF101">
+        <v>3.4</v>
+      </c>
+      <c r="AG101">
+        <v>6</v>
+      </c>
+      <c r="AH101">
+        <v>1.77</v>
+      </c>
+      <c r="AI101">
+        <v>3.45</v>
+      </c>
+      <c r="AJ101">
+        <v>6.6</v>
+      </c>
+      <c r="AK101">
+        <v>1.73</v>
+      </c>
+      <c r="AL101">
+        <v>3.45</v>
+      </c>
+      <c r="AM101">
+        <v>6</v>
+      </c>
+      <c r="AN101">
+        <v>1.7</v>
+      </c>
+      <c r="AO101">
+        <v>3.33</v>
+      </c>
+      <c r="AP101">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="102" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>266</v>
+      </c>
+      <c r="B102" t="s">
+        <v>60</v>
+      </c>
+      <c r="C102" t="s">
+        <v>44</v>
+      </c>
+      <c r="D102" s="1">
+        <v>46217</v>
+      </c>
+      <c r="E102" s="7">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>2</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="P102" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q102">
+        <v>10</v>
+      </c>
+      <c r="R102">
+        <v>10</v>
+      </c>
+      <c r="S102">
+        <v>3</v>
+      </c>
+      <c r="T102">
+        <v>2</v>
+      </c>
+      <c r="U102">
+        <v>11</v>
+      </c>
+      <c r="V102">
+        <v>12</v>
+      </c>
+      <c r="W102">
+        <v>7</v>
+      </c>
+      <c r="X102">
+        <v>1</v>
+      </c>
+      <c r="Y102">
+        <v>2</v>
+      </c>
+      <c r="Z102">
+        <v>1</v>
+      </c>
+      <c r="AA102">
+        <v>0</v>
+      </c>
+      <c r="AB102">
+        <v>0</v>
+      </c>
+      <c r="AC102">
+        <v>0.31</v>
+      </c>
+      <c r="AD102">
+        <v>1.63</v>
+      </c>
+      <c r="AE102">
+        <v>2.63</v>
+      </c>
+      <c r="AF102">
+        <v>2.9</v>
+      </c>
+      <c r="AG102">
+        <v>3.1</v>
+      </c>
+      <c r="AH102">
+        <v>2.72</v>
+      </c>
+      <c r="AI102">
+        <v>3</v>
+      </c>
+      <c r="AJ102">
+        <v>3.3</v>
+      </c>
+      <c r="AK102">
+        <v>2.63</v>
+      </c>
+      <c r="AL102">
+        <v>3.3</v>
+      </c>
+      <c r="AM102">
+        <v>3.25</v>
+      </c>
+      <c r="AN102">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AO102">
+        <v>2.95</v>
+      </c>
+      <c r="AP102">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="103" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>266</v>
+      </c>
+      <c r="B103" t="s">
+        <v>58</v>
+      </c>
+      <c r="C103" t="s">
+        <v>136</v>
+      </c>
+      <c r="D103" s="1">
+        <v>46218</v>
+      </c>
+      <c r="E103" s="7">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="G103">
+        <v>2</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>1</v>
+      </c>
+      <c r="K103">
+        <v>2</v>
+      </c>
+      <c r="P103" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q103">
+        <v>5</v>
+      </c>
+      <c r="R103">
+        <v>15</v>
+      </c>
+      <c r="S103">
+        <v>2</v>
+      </c>
+      <c r="T103">
+        <v>5</v>
+      </c>
+      <c r="U103">
+        <v>11</v>
+      </c>
+      <c r="V103">
+        <v>15</v>
+      </c>
+      <c r="W103">
+        <v>1</v>
+      </c>
+      <c r="X103">
+        <v>6</v>
+      </c>
+      <c r="Y103">
+        <v>1</v>
+      </c>
+      <c r="Z103">
+        <v>3</v>
+      </c>
+      <c r="AA103">
+        <v>0</v>
+      </c>
+      <c r="AB103">
+        <v>0</v>
+      </c>
+      <c r="AC103">
+        <v>0.52</v>
+      </c>
+      <c r="AD103">
+        <v>1.59</v>
+      </c>
+      <c r="AE103">
+        <v>2.75</v>
+      </c>
+      <c r="AF103">
+        <v>2.88</v>
+      </c>
+      <c r="AG103">
+        <v>3</v>
+      </c>
+      <c r="AH103">
+        <v>2.86</v>
+      </c>
+      <c r="AI103">
+        <v>2.92</v>
+      </c>
+      <c r="AJ103">
+        <v>3.15</v>
+      </c>
+      <c r="AK103">
+        <v>2.85</v>
+      </c>
+      <c r="AL103">
+        <v>2.9</v>
+      </c>
+      <c r="AM103">
+        <v>3.16</v>
+      </c>
+      <c r="AN103">
+        <v>2.67</v>
+      </c>
+      <c r="AO103">
+        <v>2.83</v>
+      </c>
+      <c r="AP103">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="104" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>266</v>
+      </c>
+      <c r="B104" t="s">
+        <v>60</v>
+      </c>
+      <c r="C104" t="s">
+        <v>58</v>
+      </c>
+      <c r="D104" s="1">
+        <v>46221</v>
+      </c>
+      <c r="E104" s="7">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F104">
+        <v>4</v>
+      </c>
+      <c r="G104">
+        <v>6</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>4</v>
+      </c>
+      <c r="J104">
+        <v>4</v>
+      </c>
+      <c r="K104">
+        <v>2</v>
+      </c>
+      <c r="P104" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q104">
+        <v>19</v>
+      </c>
+      <c r="R104">
+        <v>19</v>
+      </c>
+      <c r="S104">
+        <v>9</v>
+      </c>
+      <c r="T104">
+        <v>11</v>
+      </c>
+      <c r="U104">
+        <v>14</v>
+      </c>
+      <c r="V104">
+        <v>8</v>
+      </c>
+      <c r="W104">
+        <v>3</v>
+      </c>
+      <c r="X104">
+        <v>4</v>
+      </c>
+      <c r="Y104">
+        <v>0</v>
+      </c>
+      <c r="Z104">
+        <v>0</v>
+      </c>
+      <c r="AA104">
+        <v>0</v>
+      </c>
+      <c r="AB104">
+        <v>0</v>
+      </c>
+      <c r="AC104">
+        <v>2.88</v>
+      </c>
+      <c r="AD104">
+        <v>2.88</v>
+      </c>
+      <c r="AE104">
+        <v>1.7</v>
+      </c>
+      <c r="AF104">
+        <v>4.2</v>
+      </c>
+      <c r="AG104">
+        <v>4.33</v>
+      </c>
+      <c r="AH104">
+        <v>1.76</v>
+      </c>
+      <c r="AI104">
+        <v>4.5</v>
+      </c>
+      <c r="AJ104">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AK104">
+        <v>1.77</v>
+      </c>
+      <c r="AL104">
+        <v>4.33</v>
+      </c>
+      <c r="AM104">
+        <v>4.5</v>
+      </c>
+      <c r="AN104">
+        <v>1.7</v>
+      </c>
+      <c r="AO104">
+        <v>4.16</v>
+      </c>
+      <c r="AP104">
+        <v>4.3099999999999996</v>
+      </c>
+    </row>
+    <row r="105" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>266</v>
+      </c>
+      <c r="B105" t="s">
+        <v>44</v>
+      </c>
+      <c r="C105" t="s">
+        <v>136</v>
+      </c>
+      <c r="D105" s="1">
+        <v>46222</v>
+      </c>
+      <c r="E105" s="7">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>1</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="P105" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q105">
+        <v>20</v>
+      </c>
+      <c r="R105">
+        <v>2</v>
+      </c>
+      <c r="S105">
+        <v>12</v>
+      </c>
+      <c r="T105">
+        <v>0</v>
+      </c>
+      <c r="U105">
+        <v>21</v>
+      </c>
+      <c r="V105">
+        <v>25</v>
+      </c>
+      <c r="W105">
+        <v>9</v>
+      </c>
+      <c r="X105">
+        <v>4</v>
+      </c>
+      <c r="Y105">
+        <v>0</v>
+      </c>
+      <c r="Z105">
+        <v>6</v>
+      </c>
+      <c r="AA105">
+        <v>0</v>
+      </c>
+      <c r="AB105">
+        <v>1</v>
+      </c>
+      <c r="AC105">
+        <v>2.29</v>
+      </c>
+      <c r="AD105">
+        <v>0.22</v>
+      </c>
+      <c r="AE105">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AF105">
+        <v>3</v>
+      </c>
+      <c r="AG105">
+        <v>3.7</v>
+      </c>
+      <c r="AH105">
+        <v>2.34</v>
+      </c>
+      <c r="AI105">
+        <v>3.15</v>
+      </c>
+      <c r="AJ105">
+        <v>3.85</v>
+      </c>
+      <c r="AK105">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="AL105">
+        <v>3.15</v>
+      </c>
+      <c r="AM105">
+        <v>3.7</v>
+      </c>
+      <c r="AN105">
+        <v>2.23</v>
+      </c>
+      <c r="AO105">
+        <v>2.99</v>
+      </c>
+      <c r="AP105">
+        <v>3.56</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AP73">
-    <sortCondition ref="D2:D73"/>
-    <sortCondition ref="E2:E73"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AP101">
+    <sortCondition ref="D2:D101"/>
+    <sortCondition ref="E2:E101"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
